--- a/vican-catalog.xlsx
+++ b/vican-catalog.xlsx
@@ -174,7 +174,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051673_1_t20251103112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-anti-dandruff-shampoo-5204559051673.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -206,7 +206,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051642_1_t20240418112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-natural-deo-body-spray-5204559051642.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -238,7 +238,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559007274_1_t20240405112000.jpg</t>
+          <t xml:space="preserve">vican/father-son-hairstyling-box-wise-men-velvet-pomade-strong-hold-kids-velvet-pomade-5204559007274.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559007175_1_t20240405112000.jpg</t>
+          <t xml:space="preserve">vican/father-son-hairstyling-box-wise-men-velvet-pomade-medium-hold-kids-velvet-pomade-5204559007175.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -302,7 +302,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559053004_1_t20240401112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-kids-velvet-pomade-5204559053004.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051666_1_t20240401112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-velvet-pomade-strong-hold-5204559051666.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -366,7 +366,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051659_1_t20240401112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-velvet-pomade-medium-hold-5204559051659.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -398,7 +398,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051635_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-prebiotic-intimate-cleanser-gel-5204559051635.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -430,7 +430,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516226_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-eau-de-toilette-fresh-5204559516226.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516219_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-eau-de-toilette-spicy-5204559516219.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516127_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-after-shave-body-lotion-fresh-5204559516127.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516110_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-after-shave-body-lotion-spicy-5204559516110.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516028_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-bald-head-3in1-care-cream-fresh-5204559516028.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559516011_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-bald-head-3in1-care-cream-spicy-5204559516011.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515922_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-jelly-oil-fresh-5204559515922.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515915_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-jelly-oil-spicy-5204559515915.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515823_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-shower-gel-fresh-5204559515823.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515816_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-shower-gel-spicy-5204559515816.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515625_1_t20231122112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-hair-shampoo-fresh-5204559515625.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515618_1_t20231122112000.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-hair-shampoo-spicy-5204559515618.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515526_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-oil-fresh-5204559515526.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559515519_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-beard-oil-spicy-5204559515519.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559051505_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/wise-men-all-in-one-cream-5204559051505.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327774_1_t20260520113840.jpg</t>
+          <t xml:space="preserve">vican/kocostar-collagen-lifting-chin-mask-8809328327774.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327545_1_t20260520113840.jpg</t>
+          <t xml:space="preserve">vican/kocostar-hydrogel-melt-mask-thanaka-fit-8809328327545.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327668_1_t20260520113840.jpg</t>
+          <t xml:space="preserve">vican/kocostar-hydrogel-melt-mask-pdrn-fit-8809328327668.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327538_1_t20260520113840.jpg</t>
+          <t xml:space="preserve">vican/kocostar-hydrogel-melt-mask-cica-fit-8809328327538.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327484_1_t20251128112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-a-m-sunday-hydrogel-neck-mask-8809328327484.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327019_1_t20251112112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-modeling-mask-cica-8809328327019.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326999_1_t20251112112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-modeling-mask-multi-grain-8809328326999.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327071_1_t20251112112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-modeling-mask-vitamin-c-8809328327071.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328327316_1_t20250611112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-a-m-sunday-hydrogel-eye-patch-8809328327316.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326098_1_t20250516112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-a-m-sunday-happy-hydrogel-mask-8809328326098.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328322311_1_t20250227112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-white-happy-mask-8809328322311.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328321338_1_t20250124112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-princess-gold-eye-patch-8809328321338.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326784_1_t20241016112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-ultimate-face-patches-crow-8809328326784.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326791_1_t20241016112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-ultimate-face-patches-face-wrinkle-care-8809328326791.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326760_1_t20241016112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-ultimate-face-patches-forehead-wrinkle-care-8809328326760.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326777_1_t20241016112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-ultimate-face-patches-smile-lines-wrinkle-care-8809328326777.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326418_1_t20250227112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-retinol-happy-mask-8809328326418.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326395_1_t20241016112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-bakuchiol-happy-mask-8809328326395.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325312_1_t20240223112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-peach-duoduo-8809328325312.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325923_1_t20240223112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-yellow-cream-patch-8809328325923.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320447_1_t20231003133214.jpg</t>
+          <t xml:space="preserve">vican/kocostar-face-spot-mirror-patch-8809328320447.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325169_1_t20260128112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-t1-collagen-cream-8809328325169.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328326319_1_t20231027112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-happy-hair-pack-for-straight-hair-8809328326319.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328322298_1_t20231027112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-black-happy-mask-8809328322298.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328324452_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/kocostar-leg-relax-therapy-8809328324452.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320195_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-foot-peeling-pack-8809328320195.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320843_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-foot-moisture-pack-8809328320843.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320430_1_t20250508112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-hand-moisture-pack-8809328320430.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320348_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-home-salon-hair-pack-8809328320348.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328324537_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/kocostar-pearl-lip-mask-8809328324537.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328323165_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-cherry-blossom-lip-mask-8809328323165.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328320058_1_t20240620112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-princess-gold-eye-patch-micro-hole-hydrogel-8809328320058.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325596_1_t20240125112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-premium-gold-foil-triple-layer-mask-8809328325596.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328324032_1_t20250227112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-waffle-face-mask-ice-cream-8809328324032.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328324001_1_t20231122112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-waffle-face-mask-strawberry-8809328324001.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325206_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-vitamin-face-mask-8809328325206.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325213_1_t20240227112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-tea-tree-face-mask-8809328325213.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325183_1_t20250228112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-hyaluronic-face-mask-8809328325183.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/8/8809328325190_1_t20231122112000.jpg</t>
+          <t xml:space="preserve">vican/kocostar-collagen-face-mask-8809328325190.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012909006941_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-5012909006941.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8720689003339_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-8720689003339.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103911234_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-8710103911234.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103637363_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-8710103637363.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103781899_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-8710103781899.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103982685_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-ultra-air-nighttime-8710103982685.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103963882_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-ultra-soothie-8710103963882.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8720689027946_10_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-ultra-soft-8720689027946.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103949183_10_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-ultra-air-8710103949183.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103985082_10_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-natural-response-8710103985082.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103990710_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-avent-8710103990710.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058061_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-lip-nose-balm-5204559058061.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058054_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-micellar-water-5204559058054.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058047_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-face-body-lotion-5204559058047.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058030_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-foam-shampoo-5204559058030.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058023_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-wash-2-in-1-5204559058023.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058016_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-nappy-cream-5204559058016.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559058009_1_t20240415112000.jpg</t>
+          <t xml:space="preserve">vican/one-hug-baby-nappy-cream-5204559058009.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030197_1_t20260304112000.jpg</t>
+          <t xml:space="preserve">vican/cer-8-roll-on-5204559030197.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-anti-mosquito-spray-100ml-5204559030319.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030319.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030180_1_t20240405112000.jpg</t>
+          <t xml:space="preserve">vican/cer-8-active-protection-mist-5204559030180.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030609_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030609.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030623_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030623.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030616_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030616.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030135_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030135.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030173_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/cer-8-pet-spray-5204559030173.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559030142_1_t20250227112000.jpg</t>
+          <t xml:space="preserve">vican/cer-8-anti-mosquito-cream-junior-5204559030142.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-roll-on-after-bite-10ml-5204559030043.jpg</t>
+          <t xml:space="preserve">vican/cer-8-5204559030043.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-stickers-after-bite-x30-5204559030098.jpg</t>
+          <t xml:space="preserve">vican/cer-8-after-bite-stickers-5204559030098.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-ultra-protect-spray-30ml-5204559030166.jpg</t>
+          <t xml:space="preserve">vican/cer-8-mini-spray-5204559030166.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-lotion-125ml-5204559030074.jpg</t>
+          <t xml:space="preserve">vican/cer-8-lotion-5204559030074.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-strips-x24-5204559030005.jpg</t>
+          <t xml:space="preserve">vican/cer-8-microcapsules-patch-5204559030005.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-patch-junior-microcaps-x48-5204559030111.jpg</t>
+          <t xml:space="preserve">vican/cer-8-microcapsules-patch-junior-economy-pack-5204559030111.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">seasonal/cer-8-strips-x24-5204559030012.jpg</t>
+          <t xml:space="preserve">vican/cer-8-microcapsules-patch-junior-5204559030012.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062563_1_t20260304112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-bcaa-energy-plus-5204559062563.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/4/0/4011548047125_1_t20260112112000.jpg</t>
+          <t xml:space="preserve">vican/oropops-4011548047125.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629143347_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-magnesium-5060629143347.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062556_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-high-sodium-electrolytes-vitamins-caffeine-5204559062556.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062549_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-high-sodium-electrolytes-vitamins-5204559062549.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629141817_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-cranberry-probio-5060629141817.jpg</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140933_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-collagen-beauty-complex-5060629140933.jpg</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559063133_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-raw-energy-bar-5204559063133.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559063126_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-raw-energy-bar-cranberry-5204559063126.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559063119_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-raw-energy-bar-5204559063119.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559063102_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-raw-energy-bar-5204559063102.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062532_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-iron-plus-5204559062532.jpg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062525_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-magnesium-b6-5204559062525.jpg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062518_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-vitamin-c-1000-mg-5204559062518.jpg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062501_1_t20260303112000.jpg</t>
+          <t xml:space="preserve">vican/aletheia-daily-multivitamin-5204559062501.jpg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062303_1_t20231003133214.jpg</t>
+          <t xml:space="preserve">vican/liqui-vites-kids-d3-k-drops-5204559062303.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140636_1_t20251016112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-vitamin-d3-bones-teeth-immune-5060629140636.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062297_1_t20240905112000.jpg</t>
+          <t xml:space="preserve">vican/liqui-vites-kids-spray-5204559062297.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062280_1_t20240905112000.jpg</t>
+          <t xml:space="preserve">vican/liqui-vites-kids-c-5204559062280.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559062273_1_t20240905112000.jpg</t>
+          <t xml:space="preserve">vican/liqui-vites-kids-3-bubble-gum-5204559062273.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629141138_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-tummy-support-5060629141138.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009702812243_1_t20231114112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-d3-6009702812243.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009702811307_1_t20240214112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-3-6009702811307.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009802761847_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-c-6009802761847.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009802761861_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-6009802761861.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009802761823_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-bitaminh-c-6009802761823.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/6/0/6009802761809_1_t20231107112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-kids-plus-6009802761809.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140346_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-stress-relief-5060629140346.jpg</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140100_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-sweet-dreams-5060629140100.jpg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140087_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-multivitamin-complex-5060629140087.jpg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140148_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-immune-function-5060629140148.jpg</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5060629140124_1_t20250612112000.jpg</t>
+          <t xml:space="preserve">vican/chewy-vites-adults-hair-skin-nails-5060629140124.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/3/3/3323037604759_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/akileine-akilhiver-frostbite-chilblains-prevention-3323037604759.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559020860_1_t20251205112000.jpg</t>
+          <t xml:space="preserve">vican/varidoc-arnica-repair-gel-5204559020860.jpg</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559020853_1_t20240311112000.jpg</t>
+          <t xml:space="preserve">vican/varidoc-relaxing-gel-5204559020853.jpg</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559020846_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/varidoc-heavy-legs-cream-5204559020846.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559020839_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/varidoc-heavy-legs-cream-5204559020839.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201813_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-cold-sore-patch-5012654201813.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201332_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-spray-plaster-5012654201332.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5205649000267_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/a-lar-10-5205649000267.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5205649000007_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/a-lar-10-5205649000007.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202803_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-toe-protector-5012654202803.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202698_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-hard-skin-remover-pen-5012654202698.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202384_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-warm-fleece-insoles-5012654202384.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202360_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-foot-scrub-5012654202360.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202353_1_t20240330112000.jpg</t>
+          <t xml:space="preserve">vican/carnation-cracked-heel-cream-5012654202353.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202377_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-healthy-nails-5012654202377.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202322_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-soothing-foot-powder-5012654202322.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201820_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-moisturising-foot-cream-5012654201820.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201110_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-silversock-5012654201110.jpg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201530_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-pediroller-5012654201530.jpg</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201288_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-fresh-shoe-spray-5012654201288.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201264_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-cool-foot-spray-5012654201264.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200830_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-corn-callous-file-5012654200830.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654165023_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-advanced-pressure-relief-heel-pads-5012654165023.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654165016_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-advanced-pressure-relief-insoles-5012654165016.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200861_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-super-deo-insoles-5012654200861.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202926_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/pronation-5012654202926.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654203831_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-foot-mousse-5012654203831.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654203329_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-shoe-deodoriser-pouches-5012654203329.jpg</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201424_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-toenail-softening-lotion-5012654201424.jpg</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200632_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-toe-separators-5012654200632.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200625_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-toe-spreader-5012654200625.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200618_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-bunion-protector-5012654200618.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201363_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-tip-toes-gel-heel-shields-5012654201363.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201370_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-tip-toes-gel-strap-strips-5012654201370.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201356_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-tip-toes-gel-spots-5012654201356.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201240_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-tip-toes-gel-cushions-5012654201240.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200878_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-heel-grips-5012654200878.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200755_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-fleecy-padding-5012654200755.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200595_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-tofoam-5012654200595.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654142147_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-corn-pads-5012654142147.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654143021_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-bunion-pads-5012654143021.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200854_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/carnation-cushion-comfort-insoles-5012654200854.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654202940_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-fleecy-web-roll-5012654202940.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654203305_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-silky-heels-hard-skin-remover-5012654203305.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654203046_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-silky-feet-5012654203046.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201790_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-ingrowing-toenail-protector-5012654201790.jpg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201721_1_t20250704112000.jpg</t>
+          <t xml:space="preserve">vican/carnation-toe-support-5012654201721.jpg</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201608_1_t20250704112000.jpg</t>
+          <t xml:space="preserve">vican/carnation-corn-shields-5012654201608.jpg</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200847_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/carnation-hydrocolloid-blister-care-5012654200847.jpg</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654200748_1_t20250704112000.jpg</t>
+          <t xml:space="preserve">vican/carnation-hydrocolloid-corn-care-5012654200748.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654110030_1_t20240605112000.jpg</t>
+          <t xml:space="preserve">vican/carnation-blister-care-5012654110030.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201905_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/carnation-callous-caps-5012654201905.jpg</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654201714_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/carnation-corn-caps-5012654201714.jpg</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654110016_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/adaptoplast-corn-caps-5012654110016.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/0/5012654111013_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/adaptoplast-callous-caps-5012654111013.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/2/8/2803126201041_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/vein-plus-f-c-tab-450-50-mg-tab-btx60-2803126201041.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/2/8/2803126201034_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/vein-plus-f-c-tab-450-50-mg-tab-btx36-2803126201034.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8720689020121_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-s2-sensitive-8720689020121.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103805595_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-c3-premium-plaque-defence-8710103805595.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103850311_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-optimal-white-optimal-black-8710103850311.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103846734_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-protective-clean-5100-8710103846734.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103900108_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-sonic-protective-clean-4300-8710103900108.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103985471_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-sonic-2100-series-8710103985471.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103947080_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-f3-quad-stream-nozzle-8710103947080.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8710103947028_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-f1-standard-nozzle-8710103947028.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/8/7/8720689011037_1_t20241029112000.jpg</t>
+          <t xml:space="preserve">vican/philips-sonicare-cordless-power-flosser-8720689011037.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559506524_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/alcoliquid-gel-5204559506524.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559506517_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/alcoliquid-gel-5204559506517.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559050027_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/eucalyptus-vapo-5204559050027.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065113_1_t20230717095735.jpg</t>
+          <t xml:space="preserve">vican/herb-micro-filter-ultra-thin-5204559065113.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065106_1_t20250611112000.jpg</t>
+          <t xml:space="preserve">vican/herb-micro-filter-slim-5204559065106.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065090_1_t20250611112000.jpg</t>
+          <t xml:space="preserve">vican/herb-micro-filter-5204559065090.jpg</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065083_1_t20250611112000.jpg</t>
+          <t xml:space="preserve">vican/herb-micro-filter-classic-5204559065083.jpg</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065038_t20230418163921.jpg</t>
+          <t xml:space="preserve">vican/herb-spare-filters-5204559065038.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vican.gr/pub/media/catalog/product/cache/943338449f392e591c2115a51e5b080b/5/2/5204559065021_1_t20260130112000.jpg</t>
+          <t xml:space="preserve">vican/herb-cigarette-holder-12-filters-5204559065021.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
